--- a/templates/Tuck Shops.template.xlsx
+++ b/templates/Tuck Shops.template.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOHANDA Tuck" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAGORE Tuck" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Delivery" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,16 +430,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -464,17 +463,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Delivery (Rs)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>UPI</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Payment note</t>
+          <t>Delivers</t>
         </is>
       </c>
     </row>
@@ -496,12 +485,6 @@
       </c>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>mohanda@okaxis</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -520,15 +503,11 @@
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>shop@ybl</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -541,13 +520,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -563,11 +541,6 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
           <t>Diet</t>
         </is>
       </c>
@@ -581,12 +554,7 @@
           <t>Plain Cheese Sandwich Grilled</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -597,12 +565,7 @@
           <t>Veg Cheese Sandwich Grilled</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -613,12 +576,7 @@
           <t>Paneer Masala Patty / with cheese</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>40 / 60</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -629,12 +587,7 @@
           <t>Double Egg Bread Omelet (Cheese)</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>45 (65)</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -645,12 +598,7 @@
           <t>Masala Rice (Veg / Egg / Chicken / Paneer)</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>50 / 70 / 75 / 75</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -663,13 +611,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -685,11 +632,6 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
           <t>Diet</t>
         </is>
       </c>
@@ -703,12 +645,7 @@
           <t>Plain Cheese Sandwich Grilled</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -719,12 +656,7 @@
           <t>Veg Cheese Sandwich Grilled</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -735,12 +667,7 @@
           <t>Paneer Masala Patty / with cheese</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>40 / 60</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -751,12 +678,7 @@
           <t>Double Egg Bread Omelet (Cheese)</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>45 (65)</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -767,12 +689,73 @@
           <t>Masala Rice (Veg / Egg / Chicken / Paneer)</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>50 / 70 / 75 / 75</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>MOHANDA</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>MOHANDA</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>MOHANDA</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>LVH</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
